--- a/Data Engineering/Seasonal Sports/Refined Dataset.xlsx
+++ b/Data Engineering/Seasonal Sports/Refined Dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdul\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3616CBA3-0271-4DE4-9963-2888EBD88A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E90249-1116-46A4-8072-62389F78ED67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{E115D04B-62C0-43A4-B720-D6C7BA4BDA86}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E115D04B-62C0-43A4-B720-D6C7BA4BDA86}"/>
   </bookViews>
   <sheets>
     <sheet name="Coach Names" sheetId="6" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5979" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6072" uniqueCount="693">
   <si>
     <t>TeamCountry</t>
   </si>
@@ -1966,13 +1966,151 @@
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>john.smith@elitecoaching.org</t>
+  </si>
+  <si>
+    <t>maria.garcia@globalsportsacademy.com</t>
+  </si>
+  <si>
+    <t>ahmed.khan@nationalcoaching.net</t>
+  </si>
+  <si>
+    <t>li.wei@highperformance.org</t>
+  </si>
+  <si>
+    <t>emma.johnson@procoachgroup.com</t>
+  </si>
+  <si>
+    <t>noah.williams@worldathletics.org</t>
+  </si>
+  <si>
+    <t>olivia.brown@peaktraining.net</t>
+  </si>
+  <si>
+    <t>liam.jones@sportsfederation.org</t>
+  </si>
+  <si>
+    <t>ava.miller@eliteperformance.com</t>
+  </si>
+  <si>
+    <t>william.davis@coachnetwork.net</t>
+  </si>
+  <si>
+    <t>sophia.rodriguez@globalsports.org</t>
+  </si>
+  <si>
+    <t>james.martinez@highperformance.com</t>
+  </si>
+  <si>
+    <t>isabella.hernandez@nationalsports.net</t>
+  </si>
+  <si>
+    <t>benjamin.lopez@elitecoaching.org</t>
+  </si>
+  <si>
+    <t>mia.gonzalez@procoachgroup.com</t>
+  </si>
+  <si>
+    <t>lucas.wilson@worldtraining.org</t>
+  </si>
+  <si>
+    <t>amelia.anderson@sportsacademy.net</t>
+  </si>
+  <si>
+    <t>henry.thomas@eliteperformance.org</t>
+  </si>
+  <si>
+    <t>harper.taylor@globalsportsacademy.com</t>
+  </si>
+  <si>
+    <t>alexander.moore@coachnetwork.org</t>
+  </si>
+  <si>
+    <t>charlotte.jackson@highperformance.net</t>
+  </si>
+  <si>
+    <t>daniel.martin@nationalcoaching.org</t>
+  </si>
+  <si>
+    <t>evelyn.lee@procoachgroup.net</t>
+  </si>
+  <si>
+    <t>michael.perez@elitecoaching.com</t>
+  </si>
+  <si>
+    <t>abigail.thompson@worldathletics.net</t>
+  </si>
+  <si>
+    <t>ethan.white@globalsports.org</t>
+  </si>
+  <si>
+    <t>ella.harris@peaktraining.com</t>
+  </si>
+  <si>
+    <t>jacob.sanchez@sportsfederation.net</t>
+  </si>
+  <si>
+    <t>scarlett.clark@eliteperformance.org</t>
+  </si>
+  <si>
+    <t>logan.ramirez@coachnetwork.com</t>
+  </si>
+  <si>
+    <t>victoria.lewis@nationalcoaching.net</t>
+  </si>
+  <si>
+    <t>jack.robinson@globalsportsacademy.org</t>
+  </si>
+  <si>
+    <t>aria.walker@highperformance.com</t>
+  </si>
+  <si>
+    <t>aiden.young@worldtraining.net</t>
+  </si>
+  <si>
+    <t>grace.allen@elitecoaching.org</t>
+  </si>
+  <si>
+    <t>sebastian.king@procoachgroup.com</t>
+  </si>
+  <si>
+    <t>chloe.wright@sportsacademy.org</t>
+  </si>
+  <si>
+    <t>matthew.scott@coachnetwork.net</t>
+  </si>
+  <si>
+    <t>zoe.torres@globalsports.com</t>
+  </si>
+  <si>
+    <t>samuel.nguyen@peaktraining.org</t>
+  </si>
+  <si>
+    <t>natalie.hill@nationalcoaching.com</t>
+  </si>
+  <si>
+    <t>david.flores@eliteperformance.net</t>
+  </si>
+  <si>
+    <t>lily.green@worldathletics.org</t>
+  </si>
+  <si>
+    <t>jose.adams@sportsfederation.com</t>
+  </si>
+  <si>
+    <t>hannah.nelson@highperformance.org</t>
+  </si>
+  <si>
+    <t>Email ID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2106,6 +2244,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2449,8 +2593,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2826,10 +2971,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F189C90-1C69-47C9-96F3-06B160472BA3}">
-  <dimension ref="A1:C395"/>
+  <dimension ref="A1:D395"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="27.33203125" customWidth="1"/>
+    <col min="4" max="4" width="35.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>646</v>
       </c>
@@ -2839,8 +2988,11 @@
       <c r="C1" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>645</v>
       </c>
@@ -2850,8 +3002,11 @@
       <c r="C2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>644</v>
       </c>
@@ -2861,8 +3016,11 @@
       <c r="C3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>643</v>
       </c>
@@ -2872,8 +3030,11 @@
       <c r="C4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>642</v>
       </c>
@@ -2883,8 +3044,11 @@
       <c r="C5" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>641</v>
       </c>
@@ -2894,8 +3058,11 @@
       <c r="C6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>640</v>
       </c>
@@ -2905,8 +3072,11 @@
       <c r="C7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>639</v>
       </c>
@@ -2916,8 +3086,11 @@
       <c r="C8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>638</v>
       </c>
@@ -2927,8 +3100,11 @@
       <c r="C9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>637</v>
       </c>
@@ -2938,8 +3114,11 @@
       <c r="C10" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>636</v>
       </c>
@@ -2949,8 +3128,11 @@
       <c r="C11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>635</v>
       </c>
@@ -2960,8 +3142,11 @@
       <c r="C12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>634</v>
       </c>
@@ -2971,8 +3156,11 @@
       <c r="C13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>633</v>
       </c>
@@ -2982,8 +3170,11 @@
       <c r="C14" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>632</v>
       </c>
@@ -2993,8 +3184,11 @@
       <c r="C15" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>631</v>
       </c>
@@ -3004,8 +3198,11 @@
       <c r="C16" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>630</v>
       </c>
@@ -3015,8 +3212,11 @@
       <c r="C17" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>629</v>
       </c>
@@ -3026,8 +3226,11 @@
       <c r="C18" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>628</v>
       </c>
@@ -3037,8 +3240,11 @@
       <c r="C19" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>627</v>
       </c>
@@ -3048,8 +3254,11 @@
       <c r="C20" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>626</v>
       </c>
@@ -3059,8 +3268,11 @@
       <c r="C21" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>625</v>
       </c>
@@ -3070,8 +3282,11 @@
       <c r="C22" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>624</v>
       </c>
@@ -3081,8 +3296,11 @@
       <c r="C23" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>623</v>
       </c>
@@ -3092,8 +3310,11 @@
       <c r="C24" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D24" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>622</v>
       </c>
@@ -3103,8 +3324,11 @@
       <c r="C25" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>621</v>
       </c>
@@ -3114,8 +3338,11 @@
       <c r="C26" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D26" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>620</v>
       </c>
@@ -3125,8 +3352,11 @@
       <c r="C27" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D27" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>619</v>
       </c>
@@ -3136,8 +3366,11 @@
       <c r="C28" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D28" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>618</v>
       </c>
@@ -3147,8 +3380,11 @@
       <c r="C29" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D29" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>617</v>
       </c>
@@ -3158,8 +3394,11 @@
       <c r="C30" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D30" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>616</v>
       </c>
@@ -3169,8 +3408,11 @@
       <c r="C31" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D31" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>615</v>
       </c>
@@ -3180,8 +3422,11 @@
       <c r="C32" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D32" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>614</v>
       </c>
@@ -3191,8 +3436,11 @@
       <c r="C33" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D33" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>613</v>
       </c>
@@ -3202,8 +3450,11 @@
       <c r="C34" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D34" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>612</v>
       </c>
@@ -3213,8 +3464,11 @@
       <c r="C35" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D35" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>611</v>
       </c>
@@ -3224,8 +3478,11 @@
       <c r="C36" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D36" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>610</v>
       </c>
@@ -3235,8 +3492,11 @@
       <c r="C37" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D37" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>609</v>
       </c>
@@ -3246,8 +3506,11 @@
       <c r="C38" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D38" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>608</v>
       </c>
@@ -3257,8 +3520,11 @@
       <c r="C39" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D39" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>607</v>
       </c>
@@ -3268,8 +3534,11 @@
       <c r="C40" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D40" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>606</v>
       </c>
@@ -3279,8 +3548,11 @@
       <c r="C41" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D41" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>605</v>
       </c>
@@ -3290,8 +3562,11 @@
       <c r="C42" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D42" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>604</v>
       </c>
@@ -3301,8 +3576,11 @@
       <c r="C43" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D43" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>603</v>
       </c>
@@ -3312,8 +3590,11 @@
       <c r="C44" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D44" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>602</v>
       </c>
@@ -3323,8 +3604,11 @@
       <c r="C45" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D45" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>601</v>
       </c>
@@ -3334,8 +3618,11 @@
       <c r="C46" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D46" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>600</v>
       </c>
@@ -3346,7 +3633,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>599</v>
       </c>
@@ -8973,10 +9260,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73DA6130-0591-400C-B95D-55802DB3C04D}">
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="21.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>260</v>
       </c>
@@ -8989,8 +9279,11 @@
       <c r="D1" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>149</v>
       </c>
@@ -9003,8 +9296,11 @@
       <c r="D2">
         <v>64</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>110</v>
       </c>
@@ -9017,8 +9313,11 @@
       <c r="D3">
         <v>128</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>116</v>
       </c>
@@ -9031,8 +9330,11 @@
       <c r="D4">
         <v>196</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>148</v>
       </c>
@@ -9045,8 +9347,11 @@
       <c r="D5">
         <v>105</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>102</v>
       </c>
@@ -9059,8 +9364,11 @@
       <c r="D6">
         <v>2041</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>115</v>
       </c>
@@ -9073,8 +9381,11 @@
       <c r="D7">
         <v>173</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>147</v>
       </c>
@@ -9087,8 +9398,11 @@
       <c r="D8">
         <v>234</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>146</v>
       </c>
@@ -9101,8 +9415,11 @@
       <c r="D9">
         <v>288</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>145</v>
       </c>
@@ -9115,8 +9432,11 @@
       <c r="D10">
         <v>96</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>106</v>
       </c>
@@ -9129,8 +9449,11 @@
       <c r="D11">
         <v>289</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>144</v>
       </c>
@@ -9143,8 +9466,11 @@
       <c r="D12">
         <v>82</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>130</v>
       </c>
@@ -9157,8 +9483,11 @@
       <c r="D13">
         <v>249</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>124</v>
       </c>
@@ -9171,8 +9500,11 @@
       <c r="D14">
         <v>19</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>143</v>
       </c>
@@ -9185,8 +9517,11 @@
       <c r="D15">
         <v>48</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>142</v>
       </c>
@@ -9199,8 +9534,11 @@
       <c r="D16">
         <v>76</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>123</v>
       </c>
@@ -9213,8 +9551,11 @@
       <c r="D17">
         <v>201</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>141</v>
       </c>
@@ -9227,8 +9568,11 @@
       <c r="D18">
         <v>189</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>122</v>
       </c>
@@ -9241,8 +9585,11 @@
       <c r="D19">
         <v>143</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>140</v>
       </c>
@@ -9255,8 +9602,11 @@
       <c r="D20">
         <v>198</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>121</v>
       </c>
@@ -9269,8 +9619,11 @@
       <c r="D21">
         <v>215</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>105</v>
       </c>
@@ -9283,8 +9636,11 @@
       <c r="D22">
         <v>608</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>101</v>
       </c>
@@ -9297,8 +9653,11 @@
       <c r="D23">
         <v>120</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>157</v>
       </c>
@@ -9311,8 +9670,11 @@
       <c r="D24">
         <v>336</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E24" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>162</v>
       </c>
@@ -9325,8 +9687,11 @@
       <c r="D25">
         <v>384</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E25" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>104</v>
       </c>
@@ -9339,8 +9704,11 @@
       <c r="D26">
         <v>393</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>120</v>
       </c>
@@ -9353,8 +9721,11 @@
       <c r="D27">
         <v>82</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>119</v>
       </c>
@@ -9367,8 +9738,11 @@
       <c r="D28">
         <v>50</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E28" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>129</v>
       </c>
@@ -9381,8 +9755,11 @@
       <c r="D29">
         <v>72</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>128</v>
       </c>
@@ -9395,8 +9772,11 @@
       <c r="D30">
         <v>96</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E30" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>100</v>
       </c>
@@ -9409,8 +9789,11 @@
       <c r="D31">
         <v>522</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E31" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>139</v>
       </c>
@@ -9423,8 +9806,11 @@
       <c r="D32">
         <v>297</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E32" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>118</v>
       </c>
@@ -9437,8 +9823,11 @@
       <c r="D33">
         <v>350</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E33" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -9451,8 +9840,11 @@
       <c r="D34">
         <v>356</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E34" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>138</v>
       </c>
@@ -9465,8 +9857,11 @@
       <c r="D35">
         <v>80</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E35" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>137</v>
       </c>
@@ -9479,8 +9874,11 @@
       <c r="D36">
         <v>40</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E36" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>136</v>
       </c>
@@ -9493,8 +9891,11 @@
       <c r="D37">
         <v>40</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E37" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>99</v>
       </c>
@@ -9507,8 +9908,11 @@
       <c r="D38">
         <v>779</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E38" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>135</v>
       </c>
@@ -9521,8 +9925,11 @@
       <c r="D39">
         <v>172</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E39" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>114</v>
       </c>
@@ -9535,8 +9942,11 @@
       <c r="D40">
         <v>130</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E40" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>127</v>
       </c>
@@ -9549,8 +9959,11 @@
       <c r="D41">
         <v>191</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E41" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>134</v>
       </c>
@@ -9563,8 +9976,11 @@
       <c r="D42">
         <v>32</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E42" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>133</v>
       </c>
@@ -9577,8 +9993,11 @@
       <c r="D43">
         <v>110</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E43" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>117</v>
       </c>
@@ -9591,8 +10010,11 @@
       <c r="D44">
         <v>288</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E44" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>132</v>
       </c>
@@ -9605,8 +10027,11 @@
       <c r="D45">
         <v>268</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>113</v>
       </c>
@@ -9619,8 +10044,11 @@
       <c r="D46">
         <v>197</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E46" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>126</v>
       </c>
@@ -9632,6 +10060,9 @@
       </c>
       <c r="D47">
         <v>289</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
